--- a/data/models/boeing.xlsx
+++ b/data/models/boeing.xlsx
@@ -940,7 +940,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>190.47</v>
+        <v>168.18</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>12</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">B11*B12</f>
-        <v>150.585582</v>
+        <v>132.963108</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -971,7 +971,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="15" t="n">
-        <v>45.6</v>
+        <v>45.9</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>17</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B17" s="18" t="n">
         <f aca="false">B13/(B13+B14)*B10+B14/(B13+B14)*B15*(1-B16)</f>
-        <v>0.0971767210676063</v>
+        <v>0.0956081388958085</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1032,15 +1032,15 @@
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">Bear!$B$30</f>
-        <v>105.08626188093</v>
+        <v>104.367620154066</v>
       </c>
       <c r="C21" s="21" t="n">
         <f aca="false">Base!$B$30</f>
-        <v>197.085694634259</v>
+        <v>196.567285331649</v>
       </c>
       <c r="D21" s="21" t="n">
         <f aca="false">Bull!$B$30</f>
-        <v>290.625522012393</v>
+        <v>292.060886982637</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="C23" s="22" t="n">
         <f aca="false">SUMPRODUCT(B21:D21,B22:D22)</f>
-        <v>197.47079329046</v>
+        <v>197.39076945</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1071,7 +1071,7 @@
         <v>29</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>190.47</v>
+        <v>168.18</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C25" s="23" t="n">
         <f aca="false">C23/C24-1</f>
-        <v>0.0367553593240937</v>
+        <v>0.173687533892259</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C29" s="26" t="n">
         <f aca="false">(SUMPRODUCT(Base!$B$20:$K$20,1/(1+B29)^(Base!$B$17:$K$17-0.5))+Base!$K$20*(1+Base!$B$9)/(B29-Base!$B$9)/(1+B29)^9.5+Base!$B$12)/Base!$B$13</f>
-        <v>280.038438982443</v>
+        <v>273.549981328267</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="C30" s="26" t="n">
         <f aca="false">(SUMPRODUCT(Base!$B$20:$K$20,1/(1+B30)^(Base!$B$17:$K$17-0.5))+Base!$K$20*(1+Base!$B$9)/(B30-Base!$B$9)/(1+B30)^9.5+Base!$B$12)/Base!$B$13</f>
-        <v>250.518339740589</v>
+        <v>244.096912655869</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="C31" s="26" t="n">
         <f aca="false">(SUMPRODUCT(Base!$B$20:$K$20,1/(1+B31)^(Base!$B$17:$K$17-0.5))+Base!$K$20*(1+Base!$B$9)/(B31-Base!$B$9)/(1+B31)^9.5+Base!$B$12)/Base!$B$13</f>
-        <v>225.939037986812</v>
+        <v>219.58364004268</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="C32" s="26" t="n">
         <f aca="false">(SUMPRODUCT(Base!$B$20:$K$20,1/(1+B32)^(Base!$B$17:$K$17-0.5))+Base!$K$20*(1+Base!$B$9)/(B32-Base!$B$9)/(1+B32)^9.5+Base!$B$12)/Base!$B$13</f>
-        <v>205.159844275169</v>
+        <v>198.869494056975</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B11" s="28" t="n">
         <f aca="false">Summary!$B$17+B10</f>
-        <v>0.0971767210676063</v>
+        <v>0.0956081388958085</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1326,7 +1326,7 @@
         <v>48</v>
       </c>
       <c r="B12" s="27" t="n">
-        <v>-25.6</v>
+        <v>-25.2</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>17</v>
@@ -1434,13 +1434,13 @@
         <v>2</v>
       </c>
       <c r="C18" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="D18" s="27" t="n">
-        <v>9</v>
-      </c>
       <c r="E18" s="27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>11.5</v>
@@ -1484,15 +1484,15 @@
       </c>
       <c r="C20" s="30" t="n">
         <f aca="false">C18+$B$7</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20" s="30" t="n">
         <f aca="false">D18+$B$7</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="30" t="n">
         <f aca="false">E18+$B$7</f>
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="F20" s="30" t="n">
         <f aca="false">F18+$B$7</f>
@@ -1525,43 +1525,43 @@
       </c>
       <c r="B21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(B17-0.5)</f>
-        <v>0.954688536399716</v>
+        <v>0.955371705752279</v>
       </c>
       <c r="C21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(C17-0.5)</f>
-        <v>0.870131965132069</v>
+        <v>0.872001285710724</v>
       </c>
       <c r="D21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(D17-0.5)</f>
-        <v>0.793064552340655</v>
+        <v>0.795906177357862</v>
       </c>
       <c r="E21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(E17-0.5)</f>
-        <v>0.722822984768548</v>
+        <v>0.726451501318714</v>
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(F17-0.5)</f>
-        <v>0.658802698680305</v>
+        <v>0.663057780905914</v>
       </c>
       <c r="G21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(G17-0.5)</f>
-        <v>0.600452676428696</v>
+        <v>0.605196107409504</v>
       </c>
       <c r="H21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(H17-0.5)</f>
-        <v>0.547270703888455</v>
+        <v>0.552383727287241</v>
       </c>
       <c r="I21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(I17-0.5)</f>
-        <v>0.498799047938179</v>
+        <v>0.50418001443833</v>
       </c>
       <c r="J21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(J17-0.5)</f>
-        <v>0.454620516786779</v>
+        <v>0.460182793956295</v>
       </c>
       <c r="K21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(K17-0.5)</f>
-        <v>0.414354869236026</v>
+        <v>0.420024986689204</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1570,43 +1570,43 @@
       </c>
       <c r="B22" s="32" t="n">
         <f aca="false">B20*B21</f>
-        <v>3.81875414559887</v>
+        <v>3.82148682300912</v>
       </c>
       <c r="C22" s="32" t="n">
         <f aca="false">C20*C21</f>
-        <v>6.96105572105655</v>
+        <v>4.36000642855362</v>
       </c>
       <c r="D22" s="32" t="n">
         <f aca="false">D20*D21</f>
-        <v>8.72371007574721</v>
+        <v>6.36724941886289</v>
       </c>
       <c r="E22" s="32" t="n">
         <f aca="false">E20*E21</f>
-        <v>9.03528730960685</v>
+        <v>8.71741801582456</v>
       </c>
       <c r="F22" s="32" t="n">
         <f aca="false">F20*F21</f>
-        <v>8.89383643218412</v>
+        <v>8.95128004222984</v>
       </c>
       <c r="G22" s="32" t="n">
         <f aca="false">G20*G21</f>
-        <v>8.54384113290392</v>
+        <v>8.61133541232983</v>
       </c>
       <c r="H22" s="32" t="n">
         <f aca="false">H20*H21</f>
-        <v>8.16089635821902</v>
+        <v>8.23714172223752</v>
       </c>
       <c r="I22" s="32" t="n">
         <f aca="false">I20*I21</f>
-        <v>7.75048708378514</v>
+        <v>7.83409813222256</v>
       </c>
       <c r="J22" s="32" t="n">
         <f aca="false">J20*J21</f>
-        <v>7.31833301292458</v>
+        <v>7.40787273920974</v>
       </c>
       <c r="K22" s="32" t="n">
         <f aca="false">K20*K21</f>
-        <v>6.87025422484136</v>
+        <v>6.96426820001165</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B25" s="32" t="n">
         <f aca="false">SUM(B22:K22)</f>
-        <v>76.0764554968676</v>
+        <v>71.2721569344913</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B26" s="32" t="n">
         <f aca="false">K20*(1+$B$9)/($B$11-$B$9)</f>
-        <v>254.22530903329</v>
+        <v>260.303416019417</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>71</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="B27" s="32" t="n">
         <f aca="false">B26/(1+$B$11)^9.5</f>
-        <v>105.339494680977</v>
+        <v>109.33393884871</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">B25+B27</f>
-        <v>181.415950177845</v>
+        <v>180.606095783201</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">B28+$B$12</f>
-        <v>155.815950177845</v>
+        <v>155.406095783201</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">B29/$B$13</f>
-        <v>197.085694634259</v>
+        <v>196.567285331649</v>
       </c>
     </row>
   </sheetData>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B11" s="28" t="n">
         <f aca="false">Summary!$B$17+B10</f>
-        <v>0.107176721067606</v>
+        <v>0.105608138895809</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1836,7 +1836,7 @@
         <v>48</v>
       </c>
       <c r="B12" s="27" t="n">
-        <v>-25.6</v>
+        <v>-25.2</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>17</v>
@@ -1941,16 +1941,16 @@
         <v>62</v>
       </c>
       <c r="B18" s="27" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="E18" s="27" t="n">
         <v>5</v>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>6.5</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>7.5</v>
@@ -1990,19 +1990,19 @@
       </c>
       <c r="B20" s="30" t="n">
         <f aca="false">B18+$B$7</f>
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="C20" s="30" t="n">
         <f aca="false">C18+$B$7</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D20" s="30" t="n">
         <f aca="false">D18+$B$7</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" s="30" t="n">
         <f aca="false">E18+$B$7</f>
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="F20" s="30" t="n">
         <f aca="false">F18+$B$7</f>
@@ -2035,43 +2035,43 @@
       </c>
       <c r="B21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(B17-0.5)</f>
-        <v>0.950367392399345</v>
+        <v>0.95104132058756</v>
       </c>
       <c r="C21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(C17-0.5)</f>
-        <v>0.858370099655766</v>
+        <v>0.860197467013388</v>
       </c>
       <c r="D21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(D17-0.5)</f>
-        <v>0.775278312235534</v>
+        <v>0.778031055263833</v>
       </c>
       <c r="E21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(E17-0.5)</f>
-        <v>0.700229961020101</v>
+        <v>0.703713212568123</v>
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(F17-0.5)</f>
-        <v>0.632446426750101</v>
+        <v>0.636494240419516</v>
       </c>
       <c r="G21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(G17-0.5)</f>
-        <v>0.571224461927143</v>
+        <v>0.575696051817414</v>
       </c>
       <c r="H21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(H17-0.5)</f>
-        <v>0.515928894690212</v>
+        <v>0.520705330907181</v>
       </c>
       <c r="I21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(I17-0.5)</f>
-        <v>0.465986038970113</v>
+        <v>0.470967346013949</v>
       </c>
       <c r="J21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(J17-0.5)</f>
-        <v>0.420877742552952</v>
+        <v>0.425980353657954</v>
       </c>
       <c r="K21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(K17-0.5)</f>
-        <v>0.380136011301896</v>
+        <v>0.385290537100594</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2080,43 +2080,43 @@
       </c>
       <c r="B22" s="32" t="n">
         <f aca="false">B20*B21</f>
-        <v>2.37591848099836</v>
+        <v>3.32864462205646</v>
       </c>
       <c r="C22" s="32" t="n">
         <f aca="false">C20*C21</f>
-        <v>4.29185049827883</v>
+        <v>2.58059240104016</v>
       </c>
       <c r="D22" s="32" t="n">
         <f aca="false">D20*D21</f>
-        <v>5.42694818564874</v>
+        <v>3.89015527631916</v>
       </c>
       <c r="E22" s="32" t="n">
         <f aca="false">E20*E21</f>
-        <v>5.95195466867086</v>
+        <v>4.92599248797686</v>
       </c>
       <c r="F22" s="32" t="n">
         <f aca="false">F20*F21</f>
-        <v>6.00824105412596</v>
+        <v>6.04669528398541</v>
       </c>
       <c r="G22" s="32" t="n">
         <f aca="false">G20*G21</f>
-        <v>5.71967053727648</v>
+        <v>5.76444456684777</v>
       </c>
       <c r="H22" s="32" t="n">
         <f aca="false">H20*H21</f>
-        <v>5.41396383161468</v>
+        <v>5.46408595733553</v>
       </c>
       <c r="I22" s="32" t="n">
         <f aca="false">I20*I21</f>
-        <v>5.09525733805419</v>
+        <v>5.14972472365291</v>
       </c>
       <c r="J22" s="32" t="n">
         <f aca="false">J20*J21</f>
-        <v>4.76770013474824</v>
+        <v>4.8255024777881</v>
       </c>
       <c r="K22" s="32" t="n">
         <f aca="false">K20*K21</f>
-        <v>4.43536342965689</v>
+        <v>4.49550557495501</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B25" s="32" t="n">
         <f aca="false">SUM(B22:K22)</f>
-        <v>49.4868681590732</v>
+        <v>46.4713433719574</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B26" s="32" t="n">
         <f aca="false">K20*(1+$B$9)/($B$11-$B$9)</f>
-        <v>155.718818328367</v>
+        <v>158.949393314214</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>71</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B27" s="32" t="n">
         <f aca="false">B26/(1+$B$11)^9.5</f>
-        <v>59.1943304839899</v>
+        <v>61.2416971218473</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">B25+B27</f>
-        <v>108.681198643063</v>
+        <v>107.713040493805</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">B28+$B$12</f>
-        <v>83.0811986430632</v>
+        <v>82.5130404938046</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">B29/$B$13</f>
-        <v>105.08626188093</v>
+        <v>104.367620154066</v>
       </c>
     </row>
   </sheetData>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="B11" s="28" t="n">
         <f aca="false">Summary!$B$17+B10</f>
-        <v>0.0871767210676063</v>
+        <v>0.0856081388958085</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2346,7 +2346,7 @@
         <v>48</v>
       </c>
       <c r="B12" s="27" t="n">
-        <v>-25.6</v>
+        <v>-25.2</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>17</v>
@@ -2451,16 +2451,16 @@
         <v>62</v>
       </c>
       <c r="B18" s="27" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C18" s="27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D18" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="27" t="n">
-        <v>11</v>
-      </c>
       <c r="E18" s="27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="27" t="n">
         <v>14</v>
@@ -2500,19 +2500,19 @@
       </c>
       <c r="B20" s="30" t="n">
         <f aca="false">B18+$B$7</f>
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C20" s="30" t="n">
         <f aca="false">C18+$B$7</f>
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="D20" s="30" t="n">
         <f aca="false">D18+$B$7</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E20" s="30" t="n">
         <f aca="false">E18+$B$7</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F20" s="30" t="n">
         <f aca="false">F18+$B$7</f>
@@ -2545,43 +2545,43 @@
       </c>
       <c r="B21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(B17-0.5)</f>
-        <v>0.959069163844587</v>
+        <v>0.959761787506645</v>
       </c>
       <c r="C21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(C17-0.5)</f>
-        <v>0.882164918784117</v>
+        <v>0.884077553511008</v>
       </c>
       <c r="D21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(D17-0.5)</f>
-        <v>0.811427343585716</v>
+        <v>0.814361574711681</v>
       </c>
       <c r="E21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(E17-0.5)</f>
-        <v>0.746361955569556</v>
+        <v>0.750143210551077</v>
       </c>
       <c r="F21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(F17-0.5)</f>
-        <v>0.686513922811582</v>
+        <v>0.690988933920541</v>
       </c>
       <c r="G21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(G17-0.5)</f>
-        <v>0.631464884694575</v>
+        <v>0.636499404493557</v>
       </c>
       <c r="H21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(H17-0.5)</f>
-        <v>0.580830027407575</v>
+        <v>0.58630677284803</v>
       </c>
       <c r="I21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(I17-0.5)</f>
-        <v>0.534255393950305</v>
+        <v>0.540072197178231</v>
       </c>
       <c r="J21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(J17-0.5)</f>
-        <v>0.491415409838492</v>
+        <v>0.49748355583217</v>
       </c>
       <c r="K21" s="31" t="n">
         <f aca="false">1/(1+$B$11)^(K17-0.5)</f>
-        <v>0.452010607213814</v>
+        <v>0.458253340232111</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2590,43 +2590,43 @@
       </c>
       <c r="B22" s="32" t="n">
         <f aca="false">B20*B21</f>
-        <v>4.79534581922294</v>
+        <v>4.3189280437799</v>
       </c>
       <c r="C22" s="32" t="n">
         <f aca="false">C20*C21</f>
-        <v>8.82164918784117</v>
+        <v>5.74650409782155</v>
       </c>
       <c r="D22" s="32" t="n">
         <f aca="false">D20*D21</f>
-        <v>10.5485554666143</v>
+        <v>8.14361574711681</v>
       </c>
       <c r="E22" s="32" t="n">
         <f aca="false">E20*E21</f>
-        <v>11.1954293335433</v>
+        <v>10.5020049477151</v>
       </c>
       <c r="F22" s="32" t="n">
         <f aca="false">F20*F21</f>
-        <v>10.9842227649853</v>
+        <v>11.0558229427287</v>
       </c>
       <c r="G22" s="32" t="n">
         <f aca="false">G20*G21</f>
-        <v>10.6490238154893</v>
+        <v>10.7339259573793</v>
       </c>
       <c r="H22" s="32" t="n">
         <f aca="false">H20*H21</f>
-        <v>10.265283226147</v>
+        <v>10.36207633334</v>
       </c>
       <c r="I22" s="32" t="n">
         <f aca="false">I20*I21</f>
-        <v>9.83871795115453</v>
+        <v>9.94583879070988</v>
       </c>
       <c r="J22" s="32" t="n">
         <f aca="false">J20*J21</f>
-        <v>9.37557951699579</v>
+        <v>9.49135200631022</v>
       </c>
       <c r="K22" s="32" t="n">
         <f aca="false">K20*K21</f>
-        <v>8.88249970347291</v>
+        <v>9.00517619225199</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B25" s="32" t="n">
         <f aca="false">SUM(B22:K22)</f>
-        <v>95.3563067854666</v>
+        <v>89.3052450591534</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B26" s="32" t="n">
         <f aca="false">K20*(1+$B$9)/($B$11-$B$9)</f>
-        <v>354.001052992637</v>
+        <v>363.986636965557</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>71</v>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B27" s="32" t="n">
         <f aca="false">B26/(1+$B$11)^9.5</f>
-        <v>160.012230917531</v>
+        <v>166.798092189319</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B28" s="32" t="n">
         <f aca="false">B25+B27</f>
-        <v>255.368537702998</v>
+        <v>256.103337248473</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B29" s="32" t="n">
         <f aca="false">B28+$B$12</f>
-        <v>229.768537702998</v>
+        <v>230.903337248473</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="B30" s="22" t="n">
         <f aca="false">B29/$B$13</f>
-        <v>290.625522012393</v>
+        <v>292.060886982637</v>
       </c>
     </row>
   </sheetData>
